--- a/examples/Ex.8_ElectreScore_mixed_new.xlsx
+++ b/examples/Ex.8_ElectreScore_mixed_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentiunict-my.sharepoint.com/personal/zppsvn93e31c351c_studium_unict_it/Documents/PC/PhD/PAPERS/RULES Software X/Explainable-composite-indicator/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="8_{3A6B99A6-1C39-467F-BDB6-066DD8009B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E7CA444-716D-4D75-B77C-2F357D289875}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="8_{3A6B99A6-1C39-467F-BDB6-066DD8009B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96F25764-A5DD-4926-BA20-73715A3F39FB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5D75F1CB-A946-4163-9A1C-917BA0024105}"/>
   </bookViews>
